--- a/public/files/Data_By_Towns_Index/Burlington/Pemberton Township.xlsx
+++ b/public/files/Data_By_Towns_Index/Burlington/Pemberton Township.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,416 +425,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PATEL, TINU M</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GOSWAMI, RUP JYOTI</t>
+          <t>328 SALVIA ST</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ASPEN WY</t>
+          <t>Pemberton Township</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pemberton Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Goswami</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39.9778041</v>
+        <v>-74.5665181</v>
       </c>
       <c r="G2" t="n">
-        <v>-74.5331542</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PATEL, AMEET D</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BIRMINGHAM RD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>39.9687222</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-74.7107331</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PATEL, AMEET D</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>160 BIRMINGHAM RD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>39.9816592</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-74.71347109999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PATEL, AMEET D &amp; URVASHI A</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>11 VINCENTOWN RD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>39.9650213</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-74.6857344</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PATEL, AMIT &amp; URVASHI</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>30 JOHNSON CT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>39.9797683</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-74.67819489999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PATEL, AMIT &amp; URVASHI</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>65 MILLVIEW RD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>39.96757179999999</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-74.58424360000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PATEL, AMIT D &amp; URVASHI</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>585 MAGNOLIA RD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>39.918774</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-74.6379503</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PATEL, KALPESH &amp; GIRJA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>342 BROOK ST</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>39.9711629</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-74.58643099999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PATEL, TINU M</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SALVIA ST</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>39.984457</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-74.565551</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PATEL, TINU M</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>328 SALVIA ST</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
         <v>39.9848454</v>
       </c>
-      <c r="G11" t="n">
-        <v>-74.5665181</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>VIRANI, IQBAL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>301 SCRAPETOWN RD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Virani</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>39.949742</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-74.66919799999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BHATT, MRUGANK D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>251 TULIP ST</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Pemberton Township</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Bhatt</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>39.9848127</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-74.5649241</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJ5dtTgT5qwYkRajS-3xsbEvc</t>
+        </is>
       </c>
     </row>
   </sheetData>
